--- a/카드_아키타입/08_밤·살브·연고.xlsx
+++ b/카드_아키타입/08_밤·살브·연고.xlsx
@@ -3156,7 +3156,7 @@
       <row>259</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="119" name="Image 119" descr="Picture"/>
@@ -3556,7 +3556,7 @@
       <row>332</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="657225" cy="1047750"/>
+    <ext cx="647700" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="135" name="Image 135" descr="Picture"/>

--- a/카드_아키타입/08_밤·살브·연고.xlsx
+++ b/카드_아키타입/08_밤·살브·연고.xlsx
@@ -199,13 +199,8 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  <absoluteAnchor>
+    <pos x="6162675" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -223,14 +218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -248,14 +238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -273,14 +258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -298,14 +278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -323,14 +298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -348,14 +318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -373,14 +338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -398,14 +358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="3695700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -423,14 +378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="8826500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -448,14 +398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="8826500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -473,14 +418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="8826500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -498,14 +438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="8826500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -523,14 +458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="10674349"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -548,14 +478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>9</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="10674349"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -573,14 +498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>9</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="10674349"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -598,14 +518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="15417800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -623,14 +538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="15417800"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -648,14 +558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="15417800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -673,14 +578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="15417800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -698,14 +598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="17265650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -723,14 +618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>17</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="17265650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -748,14 +638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>17</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="17265650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -773,14 +658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>17</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="17265650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -798,14 +678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>28</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="29730700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -823,14 +698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>28</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="29730700"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -848,14 +718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>39</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="44043600"/>
     <ext cx="1009650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -873,14 +738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>51</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="50431700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -898,14 +758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>51</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="50431700"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -923,14 +778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>63</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="67995800"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -948,14 +798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>63</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="67995800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -973,14 +818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>63</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="67995800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -998,14 +838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>63</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="67995800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1023,14 +858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>63</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="69843650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1048,14 +878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>63</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="69843650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1073,14 +898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>63</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="69843650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1098,14 +918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>63</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="69843650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1123,14 +938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>63</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="71691500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1148,14 +958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>63</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="71691500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1173,14 +978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>63</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="71691500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1198,14 +998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>63</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="71691500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1223,14 +1018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>63</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="73539350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1248,14 +1038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>73</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="76238100"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1273,14 +1058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>73</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="76238100"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1298,14 +1078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>73</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="76238100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1323,14 +1098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>73</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="76238100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1348,14 +1118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>73</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="78085950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1373,14 +1138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>73</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="78085950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1398,14 +1158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>73</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="78085950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1423,14 +1178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>73</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="78085950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1448,14 +1198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>73</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="79933800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1473,14 +1218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>73</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="79933800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1498,14 +1238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>73</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="79933800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1523,14 +1258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>73</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="79933800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1548,14 +1278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>73</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="81781650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1573,14 +1298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>73</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="81781650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1598,14 +1318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>73</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="81781650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1623,14 +1338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>85</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="94208600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1648,14 +1358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>85</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="94208600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1673,14 +1378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>85</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="94208600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1698,14 +1398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>85</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="94208600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1723,14 +1418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>85</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="96056450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1748,14 +1438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>85</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="96056450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1773,14 +1458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>85</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="96056450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1798,14 +1478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>97</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="103441500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1823,14 +1498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>97</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="103441500"/>
     <ext cx="1533525" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1848,14 +1518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>97</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="103441500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1873,14 +1538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>97</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="103441500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1898,14 +1558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>97</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="105289350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1923,14 +1578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>97</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="105289350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1948,14 +1598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>97</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="105289350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1973,14 +1618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>97</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="105289350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1998,14 +1638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>108</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="109423200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2023,14 +1658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>108</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="109423200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2048,14 +1678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>108</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="109423200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2073,14 +1698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>108</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="109423200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2098,14 +1718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>108</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="111271050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2123,14 +1738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>120</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="115811300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2148,14 +1758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>120</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="115811300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2173,14 +1778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>120</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="115811300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2198,14 +1798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>120</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="115811300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2223,14 +1818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>120</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="117659150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2248,14 +1838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>133</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="121386600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2273,14 +1858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>133</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="121386600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2298,14 +1878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>133</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="121386600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2323,14 +1898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>133</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="121386600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2348,14 +1918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>133</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="123234450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2373,14 +1938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>144</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="134277100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2398,14 +1958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>144</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="134277100"/>
     <ext cx="1809750" cy="1447800"/>
     <pic>
       <nvPicPr>
@@ -2423,14 +1978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>144</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="134277100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2448,14 +1998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>144</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="134277100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2473,14 +2018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>144</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="136124950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2498,14 +2038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>158</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="142900400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2523,14 +2058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>158</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="142900400"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -2548,14 +2078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>158</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="142900400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2573,14 +2098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>158</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="142900400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2598,14 +2118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>158</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="144748250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2623,14 +2138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>170</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="149288500"/>
     <ext cx="1285875" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2648,14 +2158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>170</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="149288500"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -2673,14 +2178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>182</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="155473400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2698,14 +2198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>182</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="155473400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2723,14 +2218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>182</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="155473400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2748,14 +2238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>182</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="155473400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2773,14 +2258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>182</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="157321249"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2798,14 +2278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>195</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="163690300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2823,14 +2298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>195</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="163690300"/>
     <ext cx="1809750" cy="1209675"/>
     <pic>
       <nvPicPr>
@@ -2848,14 +2318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>195</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="163690300"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2873,14 +2338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>195</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="163690300"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2898,14 +2358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>195</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="165538150"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2923,14 +2378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>195</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="165538150"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2948,14 +2398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>195</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="165538150"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2973,14 +2418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>195</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="165538150"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2998,14 +2438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>195</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="167386000"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -3023,14 +2458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>207</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="171500800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3048,14 +2478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>207</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="171500800"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -3073,14 +2498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>207</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="171500800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3098,14 +2518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>207</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="171500800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3123,14 +2538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>207</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="173348650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3148,14 +2558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>216</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="179108100"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -3173,14 +2578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>216</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="179108100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3198,14 +2598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>216</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="179108100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3223,14 +2618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>216</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="179108100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3248,14 +2638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>216</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="180955950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3273,14 +2658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>216</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="180955950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3298,14 +2678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>216</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="180955950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3323,14 +2698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>228</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="189357000"/>
     <ext cx="1190625" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3348,14 +2718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>241</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="195948300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3373,14 +2738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>241</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="195948300"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -3398,14 +2758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>241</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="195948300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3423,14 +2778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>241</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="195948300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3448,14 +2798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>241</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="197796150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3473,14 +2818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>254</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="202336400"/>
     <ext cx="1657350" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3498,14 +2838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>264</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="207937100"/>
     <ext cx="1209675" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3523,14 +2858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>264</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="207937100"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -3548,14 +2878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>277</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="217779600"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3573,14 +2898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>291</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="224980500"/>
     <ext cx="1171575" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3598,14 +2918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>302</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="230987600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3623,14 +2938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>302</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="230987600"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3648,14 +2958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>302</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="230987600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3673,14 +2978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>302</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="230987600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3698,14 +2998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>302</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="232835450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3723,14 +3018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>313</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="236969300"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3748,14 +3038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>325</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="242366800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3773,14 +3058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>325</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="242366800"/>
     <ext cx="1647825" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3798,14 +3078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>325</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="242366800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3823,14 +3098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>325</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="242366800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3848,14 +3118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>325</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="244214650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3873,14 +3138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>325</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="244214650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3898,14 +3158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>325</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="244214650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3923,14 +3178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>337</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="250177300"/>
     <ext cx="1314450" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3948,14 +3198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>337</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="250177300"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -3973,14 +3218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>354</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="260629400"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -3998,14 +3238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>354</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="260629400"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -4023,14 +3258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>354</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="260629400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4048,14 +3278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>354</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="260629400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4073,14 +3298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>354</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="262477250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4098,14 +3318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>354</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="262477250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4123,14 +3338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>354</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="262477250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4148,14 +3358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>354</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="262477250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4173,14 +3378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>354</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="264325100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4198,14 +3398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>354</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="264325100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4223,14 +3418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>354</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="264325100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4248,14 +3438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>367</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="274129500"/>
     <ext cx="1390650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4273,14 +3458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>367</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="274129500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4298,14 +3478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>367</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="274129500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4323,14 +3498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>367</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="274129500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4348,14 +3518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>367</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="275977350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4373,14 +3538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>367</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="275977350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4398,14 +3558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>367</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="275977350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4423,14 +3578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>367</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="275977350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4448,7 +3598,7 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
+  </absoluteAnchor>
 </wsDr>
 </file>
 

--- a/카드_아키타입/08_밤·살브·연고.xlsx
+++ b/카드_아키타입/08_밤·살브·연고.xlsx
@@ -200,7 +200,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="6162675" y="0"/>
+    <pos x="7391400" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -220,7 +220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="0"/>
+    <pos x="9239250" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -240,7 +240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="0"/>
+    <pos x="11087100" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -260,7 +260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="0"/>
+    <pos x="12934950" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -280,7 +280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="1847850"/>
+    <pos x="7391400" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -300,7 +300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="1847850"/>
+    <pos x="9239250" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -320,7 +320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="1847850"/>
+    <pos x="11087100" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -340,7 +340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="1847850"/>
+    <pos x="12934950" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -360,7 +360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="3695700"/>
+    <pos x="7391400" y="3695700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -380,7 +380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="8826500"/>
+    <pos x="7391400" y="8826500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -400,7 +400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="8826500"/>
+    <pos x="9239250" y="8826500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -420,7 +420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="8826500"/>
+    <pos x="11087100" y="8826500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -440,7 +440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="8826500"/>
+    <pos x="12934950" y="8826500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -460,7 +460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="10674349"/>
+    <pos x="7391400" y="10674349"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -480,7 +480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="10674349"/>
+    <pos x="9239250" y="10674349"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -500,7 +500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="10674349"/>
+    <pos x="11087100" y="10674349"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -520,7 +520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="15417800"/>
+    <pos x="7391400" y="15417800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -540,7 +540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="15417800"/>
+    <pos x="9239250" y="15417800"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -560,7 +560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="15417800"/>
+    <pos x="11087100" y="15417800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -580,7 +580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="15417800"/>
+    <pos x="12934950" y="15417800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -600,7 +600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="17265650"/>
+    <pos x="7391400" y="17265650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -620,7 +620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="17265650"/>
+    <pos x="9239250" y="17265650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -640,7 +640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="17265650"/>
+    <pos x="11087100" y="17265650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -660,7 +660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="17265650"/>
+    <pos x="12934950" y="17265650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -680,7 +680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="29730700"/>
+    <pos x="7391400" y="29730700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -700,7 +700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="29730700"/>
+    <pos x="9239250" y="29730700"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -720,7 +720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="44043600"/>
+    <pos x="7391400" y="44043600"/>
     <ext cx="1009650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -740,7 +740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="50431700"/>
+    <pos x="7391400" y="50431700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -760,7 +760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="50431700"/>
+    <pos x="9239250" y="50431700"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -780,7 +780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="67995800"/>
+    <pos x="7391400" y="67995800"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -800,7 +800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="67995800"/>
+    <pos x="9239250" y="67995800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -820,7 +820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="67995800"/>
+    <pos x="11087100" y="67995800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -840,7 +840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="67995800"/>
+    <pos x="12934950" y="67995800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -860,7 +860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="69843650"/>
+    <pos x="7391400" y="69843650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -880,7 +880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="69843650"/>
+    <pos x="9239250" y="69843650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -900,7 +900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="69843650"/>
+    <pos x="11087100" y="69843650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -920,7 +920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="69843650"/>
+    <pos x="12934950" y="69843650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -940,7 +940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="71691500"/>
+    <pos x="7391400" y="71691500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -960,7 +960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="71691500"/>
+    <pos x="9239250" y="71691500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -980,7 +980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="71691500"/>
+    <pos x="11087100" y="71691500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="71691500"/>
+    <pos x="12934950" y="71691500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="73539350"/>
+    <pos x="7391400" y="73539350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="76238100"/>
+    <pos x="7391400" y="76238100"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="76238100"/>
+    <pos x="9239250" y="76238100"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="76238100"/>
+    <pos x="11087100" y="76238100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="76238100"/>
+    <pos x="12934950" y="76238100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="78085950"/>
+    <pos x="7391400" y="78085950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="78085950"/>
+    <pos x="9239250" y="78085950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="78085950"/>
+    <pos x="11087100" y="78085950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="78085950"/>
+    <pos x="12934950" y="78085950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="79933800"/>
+    <pos x="7391400" y="79933800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="79933800"/>
+    <pos x="9239250" y="79933800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="79933800"/>
+    <pos x="11087100" y="79933800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="79933800"/>
+    <pos x="12934950" y="79933800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="81781650"/>
+    <pos x="7391400" y="81781650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="81781650"/>
+    <pos x="9239250" y="81781650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="81781650"/>
+    <pos x="11087100" y="81781650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="94208600"/>
+    <pos x="7391400" y="94208600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="94208600"/>
+    <pos x="9239250" y="94208600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="94208600"/>
+    <pos x="11087100" y="94208600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="94208600"/>
+    <pos x="12934950" y="94208600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="96056450"/>
+    <pos x="7391400" y="96056450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="96056450"/>
+    <pos x="9239250" y="96056450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="96056450"/>
+    <pos x="11087100" y="96056450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="103441500"/>
+    <pos x="7391400" y="103441500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="103441500"/>
+    <pos x="9239250" y="103441500"/>
     <ext cx="1533525" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="103441500"/>
+    <pos x="11087100" y="103441500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="103441500"/>
+    <pos x="12934950" y="103441500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="105289350"/>
+    <pos x="7391400" y="105289350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="105289350"/>
+    <pos x="9239250" y="105289350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="105289350"/>
+    <pos x="11087100" y="105289350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="105289350"/>
+    <pos x="12934950" y="105289350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="109423200"/>
+    <pos x="7391400" y="109423200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="109423200"/>
+    <pos x="9239250" y="109423200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="109423200"/>
+    <pos x="11087100" y="109423200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="109423200"/>
+    <pos x="12934950" y="109423200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="111271050"/>
+    <pos x="7391400" y="111271050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="115811300"/>
+    <pos x="7391400" y="115811300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="115811300"/>
+    <pos x="9239250" y="115811300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1780,7 +1780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="115811300"/>
+    <pos x="11087100" y="115811300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1800,7 +1800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="115811300"/>
+    <pos x="12934950" y="115811300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1820,7 +1820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="117659150"/>
+    <pos x="7391400" y="117659150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1840,7 +1840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="121386600"/>
+    <pos x="7391400" y="121386600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1860,7 +1860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="121386600"/>
+    <pos x="9239250" y="121386600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1880,7 +1880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="121386600"/>
+    <pos x="11087100" y="121386600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1900,7 +1900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="121386600"/>
+    <pos x="12934950" y="121386600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1920,7 +1920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="123234450"/>
+    <pos x="7391400" y="123234450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1940,7 +1940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="134277100"/>
+    <pos x="7391400" y="134277100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1960,7 +1960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="134277100"/>
+    <pos x="9239250" y="134277100"/>
     <ext cx="1809750" cy="1447800"/>
     <pic>
       <nvPicPr>
@@ -1980,7 +1980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="134277100"/>
+    <pos x="11087100" y="134277100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2000,7 +2000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="134277100"/>
+    <pos x="12934950" y="134277100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2020,7 +2020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="136124950"/>
+    <pos x="7391400" y="136124950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2040,7 +2040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="142900400"/>
+    <pos x="7391400" y="142900400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2060,7 +2060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="142900400"/>
+    <pos x="9239250" y="142900400"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -2080,7 +2080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="142900400"/>
+    <pos x="11087100" y="142900400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2100,7 +2100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="142900400"/>
+    <pos x="12934950" y="142900400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2120,7 +2120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="144748250"/>
+    <pos x="7391400" y="144748250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2140,7 +2140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="149288500"/>
+    <pos x="7391400" y="149288500"/>
     <ext cx="1285875" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2160,7 +2160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="149288500"/>
+    <pos x="9239250" y="149288500"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -2180,7 +2180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="155473400"/>
+    <pos x="7391400" y="155473400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2200,7 +2200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="155473400"/>
+    <pos x="9239250" y="155473400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2220,7 +2220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="155473400"/>
+    <pos x="11087100" y="155473400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2240,7 +2240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="155473400"/>
+    <pos x="12934950" y="155473400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2260,7 +2260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="157321249"/>
+    <pos x="7391400" y="157321249"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2280,7 +2280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="163690300"/>
+    <pos x="7391400" y="163690300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2300,7 +2300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="163690300"/>
+    <pos x="9239250" y="163690300"/>
     <ext cx="1809750" cy="1209675"/>
     <pic>
       <nvPicPr>
@@ -2320,7 +2320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="163690300"/>
+    <pos x="11087100" y="163690300"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2340,7 +2340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="163690300"/>
+    <pos x="12934950" y="163690300"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2360,7 +2360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="165538150"/>
+    <pos x="7391400" y="165538150"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2380,7 +2380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="165538150"/>
+    <pos x="9239250" y="165538150"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2400,7 +2400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="165538150"/>
+    <pos x="11087100" y="165538150"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2420,7 +2420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="165538150"/>
+    <pos x="12934950" y="165538150"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2440,7 +2440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="167386000"/>
+    <pos x="7391400" y="167386000"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -2460,7 +2460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="171500800"/>
+    <pos x="7391400" y="171500800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2480,7 +2480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="171500800"/>
+    <pos x="9239250" y="171500800"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -2500,7 +2500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="171500800"/>
+    <pos x="11087100" y="171500800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2520,7 +2520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="171500800"/>
+    <pos x="12934950" y="171500800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2540,7 +2540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="173348650"/>
+    <pos x="7391400" y="173348650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2560,7 +2560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="179108100"/>
+    <pos x="7391400" y="179108100"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -2580,7 +2580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="179108100"/>
+    <pos x="9239250" y="179108100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2600,7 +2600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="179108100"/>
+    <pos x="11087100" y="179108100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2620,7 +2620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="179108100"/>
+    <pos x="12934950" y="179108100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2640,7 +2640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="180955950"/>
+    <pos x="7391400" y="180955950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2660,7 +2660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="180955950"/>
+    <pos x="9239250" y="180955950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2680,7 +2680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="180955950"/>
+    <pos x="11087100" y="180955950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2700,7 +2700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="189357000"/>
+    <pos x="7391400" y="189357000"/>
     <ext cx="1190625" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2720,7 +2720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="195948300"/>
+    <pos x="7391400" y="195948300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2740,7 +2740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="195948300"/>
+    <pos x="9239250" y="195948300"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -2760,7 +2760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="195948300"/>
+    <pos x="11087100" y="195948300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2780,7 +2780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="195948300"/>
+    <pos x="12934950" y="195948300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2800,7 +2800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="197796150"/>
+    <pos x="7391400" y="197796150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2820,7 +2820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="202336400"/>
+    <pos x="7391400" y="202336400"/>
     <ext cx="1657350" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2840,7 +2840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="207937100"/>
+    <pos x="7391400" y="207937100"/>
     <ext cx="1209675" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2860,7 +2860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="207937100"/>
+    <pos x="9239250" y="207937100"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -2880,7 +2880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="217779600"/>
+    <pos x="7391400" y="217779600"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2900,7 +2900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="224980500"/>
+    <pos x="7391400" y="224980500"/>
     <ext cx="1171575" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2920,7 +2920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="230987600"/>
+    <pos x="7391400" y="230987600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2940,7 +2940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="230987600"/>
+    <pos x="9239250" y="230987600"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2960,7 +2960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="230987600"/>
+    <pos x="11087100" y="230987600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2980,7 +2980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="230987600"/>
+    <pos x="12934950" y="230987600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3000,7 +3000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="232835450"/>
+    <pos x="7391400" y="232835450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3020,7 +3020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="236969300"/>
+    <pos x="7391400" y="236969300"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3040,7 +3040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="242366800"/>
+    <pos x="7391400" y="242366800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3060,7 +3060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="242366800"/>
+    <pos x="9239250" y="242366800"/>
     <ext cx="1647825" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3080,7 +3080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="242366800"/>
+    <pos x="11087100" y="242366800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3100,7 +3100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="242366800"/>
+    <pos x="12934950" y="242366800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3120,7 +3120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="244214650"/>
+    <pos x="7391400" y="244214650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3140,7 +3140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="244214650"/>
+    <pos x="9239250" y="244214650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3160,7 +3160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="244214650"/>
+    <pos x="11087100" y="244214650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3180,7 +3180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="250177300"/>
+    <pos x="7391400" y="250177300"/>
     <ext cx="1314450" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3200,7 +3200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="250177300"/>
+    <pos x="9239250" y="250177300"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -3220,7 +3220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="260629400"/>
+    <pos x="7391400" y="260629400"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -3240,7 +3240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="260629400"/>
+    <pos x="9239250" y="260629400"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -3260,7 +3260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="260629400"/>
+    <pos x="11087100" y="260629400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3280,7 +3280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="260629400"/>
+    <pos x="12934950" y="260629400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3300,7 +3300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="262477250"/>
+    <pos x="7391400" y="262477250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3320,7 +3320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="262477250"/>
+    <pos x="9239250" y="262477250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3340,7 +3340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="262477250"/>
+    <pos x="11087100" y="262477250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3360,7 +3360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="262477250"/>
+    <pos x="12934950" y="262477250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3380,7 +3380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="264325100"/>
+    <pos x="7391400" y="264325100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3400,7 +3400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="264325100"/>
+    <pos x="9239250" y="264325100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3420,7 +3420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="264325100"/>
+    <pos x="11087100" y="264325100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3440,7 +3440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="274129500"/>
+    <pos x="7391400" y="274129500"/>
     <ext cx="1390650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3460,7 +3460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="274129500"/>
+    <pos x="9239250" y="274129500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3480,7 +3480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="274129500"/>
+    <pos x="11087100" y="274129500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3500,7 +3500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="274129500"/>
+    <pos x="12934950" y="274129500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3520,7 +3520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="275977350"/>
+    <pos x="7391400" y="275977350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3540,7 +3540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="275977350"/>
+    <pos x="9239250" y="275977350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3560,7 +3560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="275977350"/>
+    <pos x="11087100" y="275977350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3580,7 +3580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="275977350"/>
+    <pos x="12934950" y="275977350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3898,7 +3898,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">

--- a/카드_아키타입/08_밤·살브·연고.xlsx
+++ b/카드_아키타입/08_밤·살브·연고.xlsx
@@ -4130,10 +4130,10 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>얼굴 빛을 부드럽게 / 얼굴을 맑게</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="n"/>
+          <t>얼굴 빛을 부드럽게 · 얼굴을 맑게</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>경화제, / 밀랍+칸데릴라왁스</t>
+          <t>경화제 · 밀랍+칸데릴라왁스</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>비정제, 유기농, / 라우르산 42%함유(모유에는 6%) / 중쇄사슬 지방산(MCT) / 빠른 흡수, 끈적임 없음 / 달콤한 향</t>
+          <t>비정제, 유기농 · 라우르산 42%함유(모유에는 6%) · 중쇄사슬 지방산(MCT) · 빠른 흡수, 끈적임 없음 · 달콤한 향</t>
         </is>
       </c>
       <c r="F18" s="19" t="inlineStr">
@@ -4478,12 +4478,12 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>아르간나무는 1999년 UNESCO로부터 유용한 세계유산으로 지정되어 보호 받고 있았습니다. / 모로코 남서부 일부 지역에서만 서식하는 아르간나무는 공기 중에 수증기를 빨아들이는 능력이 뛰어나 '사막의 목장'으로 불립니다. 보습을 주는 불포화지방산이 풍부하며 비타민E가 풍부합니다.</t>
+          <t>아르간나무는 1999년 UNESCO로부터 유용한 세계유산으로 지정되어 보호 받고 있았습니다. · 모로코 남서부 일부 지역에서만 서식하는 아르간나무는 공기 중에 수증기를 빨아들이는 능력이 뛰어나 '사막의 목장'으로 불립니다. 보습을 주는 불포화지방산이 풍부하며 비타민E가 풍부합니다.</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 베이스오일</t>
+          <t>원하는 · 베이스오일</t>
         </is>
       </c>
     </row>
@@ -4542,12 +4542,12 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>장미향이 나는 나무 심지 / 를 수증기추출법으로 추출 / 몸과 마음을 진정, 베이스 노트</t>
+          <t>장미향이 나는 나무 심지 · 를 수증기추출법으로 추출 · 몸과 마음을 진정, 베이스 노트</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>라벤더, / 로먼캐모마일 등 / 원하는 에센셜오일</t>
+          <t>라벤더 · 로먼캐모마일 등 · 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
           <t>자초, 당귀 ,감초, 감국, 금은화, 진피, 유근피, 황금 오일 담궈 유효성분을 우린 것. 진정, 보습, 각종 트러블에 효과적.</t>
         </is>
       </c>
-      <c r="F40" s="19" t="n"/>
+      <c r="F40" s="19" t="inlineStr"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="19" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>아주까리열매압착 후 얻어짐. 끈끈한 오일 입술제품 사용시 촉촉함이 오래~~</t>
+          <t>아주까리열매압착 후 얻어짐. 끈끈한 오일 입술제품 사용시 촉촉함이 오래</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>비타민E를 피마자오일양 중 일부로 대체,</t>
+          <t>비타민E를 피마자오일양 중 일부로 대체</t>
         </is>
       </c>
     </row>
@@ -5246,10 +5246,10 @@
       </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
-          <t>타마누오일은 현지어로 아티(Ati)라는 나무 열매 속 씨를 건조해서 분리합니다. / 만 살구와 같은 형태로 씨를 가지고 있습니다. 평균적으로 타마누 나무는 일년에 100킬로의 열매를 생산하고, 여기서 10킬로의 오일이 추출됩니다. / 타히티와 폴리네시아인들은 이 오일을 / 뜨거운 햇볕, 높은 습도 그리고 소금기 섞인 바다 바람으로부터 피부를 보호하기 위해 사용했습니다. / 원주민들 사이에서 타마누오일이 신이 나뭇가지 사이에 숨겨놓은 '자연의 신성한 선물' 로 여겨지고 있습니다. / 타마누오일은 소량의 칼로필릭산(지방산)과 칼로필로라이드라는 비스테로이드성 항염성분을 함유하고 있습니다. 타마누오일의 탁월한 스킨케어효능은 바로 이 성분에서 기인합니다.</t>
-        </is>
-      </c>
-      <c r="F64" s="19" t="n"/>
+          <t>타마누오일은 현지어로 아티(Ati)라는 나무 열매 속 씨를 건조해서 분리합니다. · 만 살구와 같은 형태로 씨를 가지고 있습니다. 평균적으로 타마누 나무는 일년에 100킬로의 열매를 생산하고, 여기서 10킬로의 오일이 추출됩니다. · 타히티와 폴리네시아인들은 이 오일을 · 뜨거운 햇볕, 높은 습도 그리고 소금기 섞인 바다 바람으로부터 피부를 보호하기 위해 사용했습니다. · 원주민들 사이에서 타마누오일이 신이 나뭇가지 사이에 숨겨놓은 '자연의 신성한 선물' 로 여겨지고 있습니다. · 타마누오일은 소량의 칼로필릭산(지방산)과 칼로필로라이드라는 비스테로이드성 항염성분을 함유하고 있습니다. 타마누오일의 탁월한 스킨케어효능은 바로 이 성분에서 기인합니다.</t>
+        </is>
+      </c>
+      <c r="F64" s="19" t="inlineStr"/>
     </row>
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="19" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>로즈힙오일 등 원하는 / 베이스오일</t>
+          <t>로즈힙오일 등 원하는 · 베이스오일</t>
         </is>
       </c>
     </row>
@@ -5794,12 +5794,12 @@
       </c>
       <c r="E88" s="19" t="inlineStr">
         <is>
-          <t>보습을 주는 불포화지방산이 풍부하며 / 비타민E가 풍부</t>
+          <t>보습을 주는 불포화지방산이 풍부하며 · 비타민E가 풍부</t>
         </is>
       </c>
       <c r="F88" s="19" t="inlineStr">
         <is>
-          <t>발효 마유, / 올리브오일, 포도씨오일 등 식물성 오일 등</t>
+          <t>발효 마유 · 올리브오일, 포도씨오일 등 식물성 오일 등</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t>지용성, 유비퀴논, 비타민 Q 라고 불림. / 심장, 피부 표피에 많은 양, / 20대를 기준으로 줄어듬. 전체 양의 10%처방.</t>
+          <t>지용성, 유비퀴논, 비타민 Q 라고 불림. · 심장, 피부 표피에 많은 양 · 20대를 기준으로 줄어듬. 전체 양의 10%처방.</t>
         </is>
       </c>
       <c r="F89" s="19" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t>장미향이 나는 제라늄, 심신 / 균형의 오일. / 민감, 노화피부에 사용</t>
+          <t>장미향이 나는 제라늄, 심신 · 균형의 오일. · 민감, 노화피부에 사용</t>
         </is>
       </c>
       <c r="F91" s="19" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>사람 피지성분과 비슷 / 가벼운 오일</t>
+          <t>사람 피지성분과 비슷 · 가벼운 오일</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="E114" s="19" t="inlineStr">
         <is>
-          <t>제주산 발효 마유, / 마유 중 비중이 가벼운 부분 , / 팔마톨레익산 등 불포화지방산 풍부</t>
+          <t>제주산 발효 마유 · 마유 중 비중이 가벼운 부분 · 팔마톨레익산 등 불포화지방산 풍부</t>
         </is>
       </c>
       <c r="F114" s="19" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="F115" s="19" t="inlineStr">
         <is>
-          <t>다른 버터류나 / 원하는 / 식물성오일</t>
+          <t>다른 버터류나 · 원하는 · 식물성오일</t>
         </is>
       </c>
     </row>
@@ -6453,12 +6453,12 @@
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t>장미향이 나는 제라늄 에센셜오일, / 모든 피부</t>
+          <t>장미향이 나는 제라늄 에센셜오일 · 모든 피부</t>
         </is>
       </c>
       <c r="F117" s="19" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>연핑크색 원하면 / 발효동백오일 84g, / 자초오일 6g 로 대체</t>
+          <t>연핑크색 원하면 · 발효동백오일 84g · 자초오일 6g 로 대체</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="E139" s="19" t="inlineStr">
         <is>
-          <t>자초근을 호호바, 해바라기,비타민E에 인퓨즈한 오일, / 붉은 색</t>
+          <t>자초근을 호호바, 해바라기,비타민E에 인퓨즈한 오일 · 붉은 색</t>
         </is>
       </c>
       <c r="F139" s="19" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="F140" s="19" t="inlineStr">
         <is>
-          <t>비타민E를 피마자오일양 중 일부로 대체,</t>
+          <t>비타민E를 피마자오일양 중 일부로 대체</t>
         </is>
       </c>
     </row>
@@ -6967,12 +6967,12 @@
       </c>
       <c r="E142" s="19" t="inlineStr">
         <is>
-          <t>노화예방, 탄력도움, / 산화방지제</t>
+          <t>노화예방, 탄력도움 · 산화방지제</t>
         </is>
       </c>
       <c r="F142" s="19" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -7424,12 +7424,12 @@
       </c>
       <c r="E165" s="19" t="inlineStr">
         <is>
-          <t>들장미 열매씨 추출, / 풍부한 비타민</t>
+          <t>들장미 열매씨 추출 · 풍부한 비타민</t>
         </is>
       </c>
       <c r="F165" s="19" t="inlineStr">
         <is>
-          <t>아르간, / 마룰라 등</t>
+          <t>아르간 · 마룰라 등</t>
         </is>
       </c>
     </row>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="E169" s="19" t="inlineStr">
         <is>
-          <t>볼륨, 지모추출물, / 지방증식</t>
+          <t>볼륨, 지모추출물 · 지방증식</t>
         </is>
       </c>
       <c r="F169" s="19" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="F170" s="19" t="inlineStr">
         <is>
-          <t>로즈3% in 호호바오일 / 10방울 또는 / 로즈우드, 로즈제라늄 등 / 원하는 에센셜오일</t>
+          <t>로즈3% in 호호바오일 · 10방울 또는 · 로즈우드, 로즈제라늄 등 · 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="E180" s="10" t="inlineStr">
         <is>
-          <t>피지성분과 비슷, / 빠른흡수</t>
+          <t>피지성분과 비슷 · 빠른흡수</t>
         </is>
       </c>
       <c r="F180" s="10" t="inlineStr">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="F184" s="10" t="inlineStr">
         <is>
-          <t>브라이트닝. / 로즈파워 블렌딩오일</t>
+          <t>브라이트닝. · 로즈파워 블렌딩오일</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="F196" s="19" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="F209" s="10" t="inlineStr">
         <is>
-          <t>정제밀랍, / 칸데릴라왁스</t>
+          <t>정제밀랍 · 칸데릴라왁스</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="F210" s="10" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8628,7 @@
       </c>
       <c r="E220" s="19" t="inlineStr">
         <is>
-          <t>모로코에서만 나는 아르간나무열매, / 토코페롤, 폴리페놀, 스쿠알렌 등 다량함유, / 노화, 민감, 재생 등 사용</t>
+          <t>모로코에서만 나는 아르간나무열매 · 토코페롤, 폴리페놀, 스쿠알렌 등 다량함유 · 노화, 민감, 재생 등 사용</t>
         </is>
       </c>
       <c r="F220" s="19" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="E224" s="19" t="inlineStr">
         <is>
-          <t>장미꽃잎을 용매추출, 고농축, / 여성들에게는 피부, 생식기에 좋음.아로마테라피효과</t>
+          <t>장미꽃잎을 용매추출, 고농축 · 여성들에게는 피부, 생식기에 좋음.아로마테라피효과</t>
         </is>
       </c>
       <c r="F224" s="19" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="F234" s="10" t="inlineStr">
         <is>
-          <t>로먼캐모마일EO / 등원하는 에센셜오일</t>
+          <t>로먼캐모마일EO · 등원하는 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="E246" s="19" t="inlineStr">
         <is>
-          <t>넣지 않으면 코코넛향이 은은함 / 강한 향을 원하면 원하는 식향을 추가</t>
+          <t>넣지 않으면 코코넛향이 은은함 · 강한 향을 원하면 원하는 식향을 추가</t>
         </is>
       </c>
       <c r="F246" s="19" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="E256" s="10" t="inlineStr">
         <is>
-          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) / 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
+          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) · 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
         </is>
       </c>
       <c r="F256" s="10" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="E258" s="10" t="inlineStr">
         <is>
-          <t>바다의 이슬이란 뜻에서 유래, / 혈액순환에 도움</t>
+          <t>바다의 이슬이란 뜻에서 유래 · 혈액순환에 도움</t>
         </is>
       </c>
       <c r="F258" s="10" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="F259" s="10" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -9636,12 +9636,12 @@
       </c>
       <c r="E269" s="19" t="inlineStr">
         <is>
-          <t>콩과식물, 사람피지성분과 가장흡사, / 가벼운 사용감. 흡수력탁월</t>
+          <t>콩과식물, 사람피지성분과 가장흡사 · 가벼운 사용감. 흡수력탁월</t>
         </is>
       </c>
       <c r="F269" s="19" t="inlineStr">
         <is>
-          <t>마카다미아넛, / 아몬드오일</t>
+          <t>마카다미아넛 · 아몬드오일</t>
         </is>
       </c>
     </row>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="F271" s="19" t="inlineStr">
         <is>
-          <t>제라늄EO, 시나몬EO, / 페파민트EO 등 벌레퇴치효과있는 것</t>
+          <t>제라늄EO, 시나몬EO · 페파민트EO 등 벌레퇴치효과있는 것</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="E272" s="19" t="inlineStr">
         <is>
-          <t>리모넨, 레몬껍질오일, 항균, 상큼,</t>
+          <t>리모넨, 레몬껍질오일, 항균, 상큼</t>
         </is>
       </c>
       <c r="F272" s="19" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="E273" s="19" t="inlineStr">
         <is>
-          <t>멘톨, 박하일종,</t>
+          <t>멘톨, 박하일종</t>
         </is>
       </c>
       <c r="F273" s="19" t="inlineStr">
         <is>
-          <t>티트리(항균), / 스피아민트 등</t>
+          <t>티트리(항균) · 스피아민트 등</t>
         </is>
       </c>
     </row>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="E283" s="10" t="inlineStr">
         <is>
-          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) / 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
+          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) · 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
         </is>
       </c>
       <c r="F283" s="10" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="E286" s="10" t="inlineStr">
         <is>
-          <t>6 IN ONE / 피부결 개선, 보습, 맑은 피부, / 윤기, 영양공급, 피부정화 / 스크럽제를 만들기 위한 / 최적의 베이스</t>
+          <t>6 IN ONE · 피부결 개선, 보습, 맑은 피부 · 윤기, 영양공급, 피부정화 · 스크럽제를 만들기 위한 · 최적의 베이스</t>
         </is>
       </c>
       <c r="F286" s="10" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="E293" s="19" t="inlineStr">
         <is>
-          <t>들장미열매 압착 혹은 용매추출, / 주름, 노화피부관리에사용함</t>
+          <t>들장미열매 압착 혹은 용매추출 · 주름, 노화피부관리에사용함</t>
         </is>
       </c>
       <c r="F293" s="19" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="E295" s="19" t="inlineStr">
         <is>
-          <t>피부에 자연적으로 존재하는 성분, / 피부결 개선, 보습 / 장벽 강화, 우수한 흡수력</t>
+          <t>피부에 자연적으로 존재하는 성분 · 피부결 개선, 보습 · 장벽 강화, 우수한 흡수력</t>
         </is>
       </c>
       <c r="F295" s="19" t="inlineStr">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="F298" s="19" t="inlineStr">
         <is>
-          <t>로즈3% in 호호바오일 / 10방울 또는 / 로즈우드, 로즈제라늄 등 / 원하는 에센셜오일</t>
+          <t>로즈3% in 호호바오일 · 10방울 또는 · 로즈우드, 로즈제라늄 등 · 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10427,7 @@
       </c>
       <c r="E306" s="10" t="inlineStr">
         <is>
-          <t>6 IN ONE / 피부결 개선, 보습, 맑은 피부, / 윤기, 영양공급, 피부정화 / 스크럽제를 만들기 위한 / 최적의 베이스</t>
+          <t>6 IN ONE · 피부결 개선, 보습, 맑은 피부 · 윤기, 영양공급, 피부정화 · 스크럽제를 만들기 위한 · 최적의 베이스</t>
         </is>
       </c>
       <c r="F306" s="10" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="F308" s="10" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="E321" s="19" t="inlineStr">
         <is>
-          <t>들장미열매 압착 혹은 용매추출, / 주름, 노화피부관리에사용함</t>
+          <t>들장미열매 압착 혹은 용매추출 · 주름, 노화피부관리에사용함</t>
         </is>
       </c>
       <c r="F321" s="19" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="F322" s="19" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E323" s="19" t="inlineStr">
         <is>
-          <t>6 IN ONE / 피부결 개선, 보습, 맑은 피부, / 윤기, 영양공급, 피부정화 / 스크럽제를 만들기 위한 / 최적의 베이스</t>
+          <t>6 IN ONE · 피부결 개선, 보습, 맑은 피부 · 윤기, 영양공급, 피부정화 · 스크럽제를 만들기 위한 · 최적의 베이스</t>
         </is>
       </c>
       <c r="F323" s="19" t="inlineStr">
@@ -10955,10 +10955,10 @@
       </c>
       <c r="E331" s="10" t="inlineStr">
         <is>
-          <t>자초와, 당귀를 기본으로 한약재8종을 오일에 담궈 유효성분을 우린 것 / 직접만들기 방법과 허브누리 자운유오일을 이용해 만들기 방법이 있습니다.</t>
-        </is>
-      </c>
-      <c r="F331" s="10" t="n"/>
+          <t>자초와, 당귀를 기본으로 한약재8종을 오일에 담궈 유효성분을 우린 것 · 직접만들기 방법과 허브누리 자운유오일을 이용해 만들기 방법이 있습니다.</t>
+        </is>
+      </c>
+      <c r="F331" s="10" t="inlineStr"/>
     </row>
     <row r="332" ht="48" customHeight="1">
       <c r="A332" s="10" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="E332" s="10" t="inlineStr">
         <is>
-          <t>벌집에서 채취, / 단단하게 굳히는 역할</t>
+          <t>벌집에서 채취 · 단단하게 굳히는 역할</t>
         </is>
       </c>
       <c r="F332" s="10" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="F333" s="10" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -11181,7 +11181,7 @@
       </c>
       <c r="E343" s="19" t="inlineStr">
         <is>
-          <t>월견초 종자유, / 감마리놀린산 다량함유,</t>
+          <t>월견초 종자유 · 감마리놀린산 다량함유</t>
         </is>
       </c>
       <c r="F343" s="19" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="E344" s="19" t="inlineStr">
         <is>
-          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) / 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
+          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) · 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
         </is>
       </c>
       <c r="F344" s="19" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="E355" s="10" t="inlineStr">
         <is>
-          <t>올레인산이 올리브오일의 4배 / 비타민E함량이 2배.탁월한 보습효과</t>
+          <t>올레인산이 올리브오일의 4배 · 비타민E함량이 2배.탁월한 보습효과</t>
         </is>
       </c>
       <c r="F355" s="10" t="inlineStr">
         <is>
-          <t>유기농 / 햄프씨드오일</t>
+          <t>유기농 · 햄프씨드오일</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="F357" s="10" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="E368" s="19" t="inlineStr">
         <is>
-          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) / 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
+          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) · 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
         </is>
       </c>
       <c r="F368" s="19" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="E370" s="19" t="inlineStr">
         <is>
-          <t>월견초 종자유, / 감마리놀린산 다량함유,</t>
+          <t>월견초 종자유 · 감마리놀린산 다량함유</t>
         </is>
       </c>
       <c r="F370" s="19" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="E371" s="19" t="inlineStr">
         <is>
-          <t>올레인산 다량함유, 피부장벽강화, 항산화효과 베이비, / 민감 성피부</t>
+          <t>올레인산 다량함유, 피부장벽강화, 항산화효과 베이비 · 민감 성피부</t>
         </is>
       </c>
       <c r="F371" s="19" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="E372" s="19" t="inlineStr">
         <is>
-          <t>6 IN ONE / 피부결 개선, 보습, 맑은 피부, / 윤기, 영양공급, 피부정화 / 스크럽제를 만들기 위한 / 최적의 베이스</t>
+          <t>6 IN ONE · 피부결 개선, 보습, 맑은 피부 · 윤기, 영양공급, 피부정화 · 스크럽제를 만들기 위한 · 최적의 베이스</t>
         </is>
       </c>
       <c r="F372" s="19" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="F374" s="19" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="F376" s="19" t="inlineStr">
         <is>
-          <t>레몬에센셜오일 등 / 원하는 에센셜오일</t>
+          <t>레몬에센셜오일 등 · 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -12109,12 +12109,12 @@
       </c>
       <c r="E385" s="10" t="inlineStr">
         <is>
-          <t>금잔화 인퓨즈오일. / 문제성 피부를 진정시켜주고 / 개선에 도움을 줌.</t>
+          <t>금잔화 인퓨즈오일. · 문제성 피부를 진정시켜주고 · 개선에 도움을 줌.</t>
         </is>
       </c>
       <c r="F385" s="10" t="inlineStr">
         <is>
-          <t>자운고, / 타마누오일</t>
+          <t>자운고 · 타마누오일</t>
         </is>
       </c>
     </row>
@@ -12173,12 +12173,12 @@
       </c>
       <c r="E387" s="10" t="inlineStr">
         <is>
-          <t>3% 소염, 진통작용, 바하, 지용성, 아스피린 성분, 두꺼운 각질을 천천히 제거 화장품 성분이 잘 흡수되도록 도와줌,</t>
+          <t>3% 소염, 진통작용, 바하, 지용성, 아스피린 성분, 두꺼운 각질을 천천히 제거 화장품 성분이 잘 흡수되도록 도와줌</t>
         </is>
       </c>
       <c r="F387" s="10" t="inlineStr">
         <is>
-          <t>임산부와 30개월 미만 사용금지. / 30개월 이하의 경우 살리실산과 멘톨를 빼고 만들어주세요.</t>
+          <t>임산부와 30개월 미만 사용금지. · 30개월 이하의 경우 살리실산과 멘톨를 빼고 만들어주세요.</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="F388" s="10" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -12408,7 +12408,7 @@
       </c>
       <c r="E399" s="19" t="inlineStr">
         <is>
-          <t>포화지방산과 불포화지방산의 균형 잡힌 조성을 갖춘 코포아수 씨드 버터는 낮은 융점(약 30℃)이 특징이며 / 피부에 발랐을 때 부드럽고 빠르게 흡수되는 소프트 Solid 타입의 버터입니다.</t>
+          <t>포화지방산과 불포화지방산의 균형 잡힌 조성을 갖춘 코포아수 씨드 버터는 낮은 융점(약 30℃)이 특징이며 · 피부에 발랐을 때 부드럽고 빠르게 흡수되는 소프트 Solid 타입의 버터입니다.</t>
         </is>
       </c>
       <c r="F399" s="19" t="inlineStr">
@@ -12440,7 +12440,7 @@
       </c>
       <c r="E400" s="19" t="inlineStr">
         <is>
-          <t>올레인 산과 리놀레산이 다량 함유된 불포화 지방산 성분이 풍부하여 고기능성 오일임을 인정받고 있으며, / 특히 리놀레산은 피부를 부드럽게 하고 건강하게 하는데 효과적입니다</t>
+          <t>올레인 산과 리놀레산이 다량 함유된 불포화 지방산 성분이 풍부하여 고기능성 오일임을 인정받고 있으며 · 특히 리놀레산은 피부를 부드럽게 하고 건강하게 하는데 효과적입니다</t>
         </is>
       </c>
       <c r="F400" s="19" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="F401" s="19" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
